--- a/templates/panels/all-panels.xlsx
+++ b/templates/panels/all-panels.xlsx
@@ -7121,7 +7121,7 @@
         <v>SAPE</v>
       </c>
       <c r="B11" t="str">
-        <v>n/a</v>
+        <v>1</v>
       </c>
       <c r="C11" t="str">
         <v>n/a</v>
@@ -15281,7 +15281,7 @@
         <v>SAPE</v>
       </c>
       <c r="B11" t="str">
-        <v>n/a</v>
+        <v>1</v>
       </c>
       <c r="C11" t="str">
         <v>n/a</v>
